--- a/webhook/Layout WebHook.xlsx
+++ b/webhook/Layout WebHook.xlsx
@@ -246,6 +246,8 @@
 1 – NF-e
 2 – NFC-e
 4 – NFS-e
+5 – CT-e
+11 – NFCom
 12 – GNRE
 14 – Certificado Digital</t>
   </si>
@@ -553,10 +555,10 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1120,7 +1122,7 @@
       <c r="H13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="17" t="s">
         <v>51</v>
       </c>
       <c r="J13" s="16" t="s">
@@ -1152,7 +1154,7 @@
       <c r="H14" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="16" t="s">
@@ -1230,7 +1232,7 @@
       <c r="H17" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="21" t="s">
         <v>61</v>
       </c>
       <c r="J17" s="17" t="s">
@@ -1263,14 +1265,14 @@
       <c r="H18" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="21" t="s">
         <v>66</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19">
       <c r="A19" s="15">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1296,7 +1298,7 @@
       <c r="H19" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="23" t="s">
+      <c r="I19" s="22" t="s">
         <v>70</v>
       </c>
       <c r="J19" s="16" t="s">
@@ -1440,7 +1442,7 @@
       <c r="H24" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="21" t="s">
         <v>83</v>
       </c>
       <c r="J24" s="17" t="s">
@@ -1473,7 +1475,7 @@
       <c r="H25" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I25" s="22" t="s">
+      <c r="I25" s="21" t="s">
         <v>87</v>
       </c>
       <c r="J25" s="17" t="s">
